--- a/word-monitor-sitemap/report/history/keyword-table-20260711-160008.xlsx
+++ b/word-monitor-sitemap/report/history/keyword-table-20260711-160008.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$10</definedName>
@@ -34,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -65,7 +75,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-11T16:04:37</t>
+          <t>2026-07-11T20:57:52</t>
         </is>
       </c>
     </row>
@@ -541,16 +560,16 @@
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,52 +585,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>score(simWindowVolume*cpc/kd)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sim)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sim)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sim)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sem)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sem)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sem)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>gefeiKD</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sourcePresence(SIM/SEM)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>score(simWindowVolume*cpc/kd)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sim)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sim)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sim)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sem)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sem)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sem)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>gefeiKD</t>
         </is>
       </c>
     </row>
@@ -650,54 +669,38 @@
 https://www.crazygames.com/vn/game/green</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>54518.094</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>833610</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1257960</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>54518.094</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>833610.0</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>1257960.0</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>4.74</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
     </row>
@@ -726,54 +729,38 @@
 https://www.crazygames.com/vn/game/unscrambled</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>36.685106</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4660</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>183690</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>unscrambled</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>36.685106</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>4660.0</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>183690.0</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>70.5</t>
         </is>
       </c>
     </row>
@@ -788,34 +775,28 @@
           <t>https://www.coolmathgames.com/0-dd-2k-shoot</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>dd 2k shoot</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>23.1</t>
         </is>
       </c>
     </row>
@@ -830,42 +811,32 @@
           <t>https://poki.com/en/g/backrooms-recovery</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="4" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="8" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>backrooms recovery</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1260.0</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>47.3</t>
         </is>
       </c>
     </row>
@@ -894,30 +865,26 @@
 https://www.crazygames.com/vn/game/block-sort---jigsaw-puzzle-journey</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="8" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>block sort jigsaw puzzle journey</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>63.6</t>
         </is>
       </c>
     </row>
@@ -949,30 +916,26 @@
 https://www.crazygames.com/vn/game/downhill-racer-bvk</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="8" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>downhill racer bvk</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>33.8</t>
         </is>
       </c>
     </row>
@@ -998,30 +961,26 @@
 https://www.crazygames.com/vn/game/nightfall-survivors-imo</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>nightfall survivors imo</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>32.6</t>
         </is>
       </c>
     </row>
@@ -1053,30 +1012,26 @@
 https://www.crazygames.com/vn/game/pixel-world-uyv</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="8" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>pixel world uyv</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>33.6</t>
         </is>
       </c>
     </row>
@@ -1105,30 +1060,26 @@
 https://www.crazygames.com/vn/game/the-flowers-merge-and-sell-bouquets</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>the flowers merge and sell bouquets</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>47.3</t>
         </is>
       </c>
     </row>
